--- a/data/gravel/Wilde Dream Engine Ti 2025.xlsx
+++ b/data/gravel/Wilde Dream Engine Ti 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F002864F-19E3-F146-A5AA-7340B372FB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B103AB0-36BC-544B-9C41-869D8D92AA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5560" yWindow="2180" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31700" yWindow="-19260" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>a8:h34</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1230,22 +1233,28 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>47</v>
+        <f>2.6*25.4</f>
+        <v>66.039999999999992</v>
       </c>
       <c r="D29">
-        <v>47</v>
+        <f t="shared" ref="D29:H29" si="0">2.6*25.4</f>
+        <v>66.039999999999992</v>
       </c>
       <c r="E29">
-        <v>38</v>
+        <f t="shared" si="0"/>
+        <v>66.039999999999992</v>
       </c>
       <c r="F29">
-        <v>38</v>
+        <f t="shared" si="0"/>
+        <v>66.039999999999992</v>
       </c>
       <c r="G29">
-        <v>38</v>
+        <f t="shared" si="0"/>
+        <v>66.039999999999992</v>
       </c>
       <c r="H29">
-        <v>38</v>
+        <f t="shared" si="0"/>
+        <v>66.039999999999992</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -1256,22 +1265,28 @@
         <v>29</v>
       </c>
       <c r="C30">
-        <v>50</v>
+        <f>2.6*25.4</f>
+        <v>66.039999999999992</v>
       </c>
       <c r="D30">
-        <v>50</v>
+        <f t="shared" ref="D30:H30" si="1">2.6*25.4</f>
+        <v>66.039999999999992</v>
       </c>
       <c r="E30">
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>66.039999999999992</v>
       </c>
       <c r="F30">
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>66.039999999999992</v>
       </c>
       <c r="G30">
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>66.039999999999992</v>
       </c>
       <c r="H30">
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>66.039999999999992</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -1290,19 +1305,19 @@
         <v>163.82999999999998</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" ref="E31:H31" si="0">AVERAGE(E33,D34)</f>
+        <f t="shared" ref="E31:H31" si="2">AVERAGE(E33,D34)</f>
         <v>170.18</v>
       </c>
       <c r="F31" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>175.26</v>
       </c>
       <c r="G31" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>181.61</v>
       </c>
       <c r="H31" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>186.69</v>
       </c>
       <c r="I31" s="3"/>
@@ -1319,23 +1334,23 @@
         <v>163.82999999999998</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" ref="D32:H32" si="1">E31</f>
+        <f t="shared" ref="D32:H32" si="3">E31</f>
         <v>170.18</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>175.26</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>181.61</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>186.69</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I32" s="3"/>
@@ -1349,23 +1364,23 @@
         <v>154.94</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:H34" si="2">D35*2.54</f>
+        <f t="shared" ref="D33:H34" si="4">D35*2.54</f>
         <v>165.1</v>
       </c>
       <c r="E33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>170.18</v>
       </c>
       <c r="F33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>175.26</v>
       </c>
       <c r="G33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>182.88</v>
       </c>
       <c r="H33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>185.42000000000002</v>
       </c>
     </row>
@@ -1378,23 +1393,23 @@
         <v>162.56</v>
       </c>
       <c r="D34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>170.18</v>
       </c>
       <c r="E34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>175.26</v>
       </c>
       <c r="F34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>180.34</v>
       </c>
       <c r="G34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>187.96</v>
       </c>
       <c r="H34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>193.04</v>
       </c>
     </row>
@@ -1587,6 +1602,9 @@
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Wilde Dream Engine Ti 2025.xlsx
+++ b/data/gravel/Wilde Dream Engine Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B103AB0-36BC-544B-9C41-869D8D92AA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527F5977-DD69-954A-BA33-76C07F00DFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31700" yWindow="-19260" windowWidth="26020" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2900" yWindow="720" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>https://www.wildebikes.com/cdn/shop/products/IMG_0371_8cb872d8-aaf4-4786-a5a2-09bf783f09c2_5293x.jpg?v=1669402923</t>
   </si>
 </sst>
 </file>
@@ -767,6 +770,11 @@
         <v>112</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Wilde Dream Engine Ti 2025.xlsx
+++ b/data/gravel/Wilde Dream Engine Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527F5977-DD69-954A-BA33-76C07F00DFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808C13E2-6EC1-EA46-ADF6-6AC7FE452FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2900" yWindow="720" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -365,9 +365,6 @@
     <t>titanium</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Dream Engine Ti</t>
   </si>
   <si>
@@ -381,6 +378,15 @@
   </si>
   <si>
     <t>https://www.wildebikes.com/cdn/shop/products/IMG_0371_8cb872d8-aaf4-4786-a5a2-09bf783f09c2_5293x.jpg?v=1669402923</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota, USA</t>
   </si>
 </sst>
 </file>
@@ -724,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -743,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -767,12 +773,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -780,7 +786,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1612,7 +1618,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1751,7 +1757,15 @@
         <v>68</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>116</v>
+      </c>
+      <c r="B75" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Wilde Dream Engine Ti 2025.xlsx
+++ b/data/gravel/Wilde Dream Engine Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808C13E2-6EC1-EA46-ADF6-6AC7FE452FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEAE811-DE2F-2547-8566-C6B625A045AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -269,12 +269,6 @@
     <t>external</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -371,9 +365,6 @@
     <t>https://www.wildebikes.com/collections/bikepacking-bikes/products/dream-engine-titanium</t>
   </si>
   <si>
-    <t>a8:h34</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -387,6 +378,9 @@
   </si>
   <si>
     <t>Minneapolis, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>a8:h32</t>
   </si>
 </sst>
 </file>
@@ -730,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -749,7 +743,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -773,12 +767,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -786,7 +780,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -794,25 +788,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>82</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>83</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>84</v>
-      </c>
-      <c r="G8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -820,7 +814,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9">
         <v>68</v>
@@ -846,7 +840,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C10">
         <v>74</v>
@@ -872,7 +866,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C11">
         <v>160</v>
@@ -898,7 +892,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C12">
         <v>345</v>
@@ -924,7 +918,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C13">
         <v>525</v>
@@ -950,7 +944,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C14">
         <v>576.4</v>
@@ -976,7 +970,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C15">
         <v>355</v>
@@ -1002,7 +996,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C16">
         <v>425</v>
@@ -1028,7 +1022,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>406</v>
@@ -1054,7 +1048,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C18">
         <v>55.5</v>
@@ -1080,7 +1074,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C19">
         <v>81</v>
@@ -1106,7 +1100,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C20">
         <v>733</v>
@@ -1132,7 +1126,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C21">
         <v>30</v>
@@ -1158,7 +1152,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C22">
         <v>63</v>
@@ -1311,15 +1305,15 @@
         <v>30</v>
       </c>
       <c r="C31" s="3">
-        <f>C33</f>
+        <f>C33*2.54</f>
         <v>154.94</v>
       </c>
       <c r="D31" s="3">
-        <f>AVERAGE(D33,C34)</f>
-        <v>163.82999999999998</v>
+        <f t="shared" ref="D31:H32" si="2">D33*2.54</f>
+        <v>165.1</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" ref="E31:H31" si="2">AVERAGE(E33,D34)</f>
+        <f t="shared" si="2"/>
         <v>170.18</v>
       </c>
       <c r="F31" s="3">
@@ -1328,11 +1322,11 @@
       </c>
       <c r="G31" s="3">
         <f t="shared" si="2"/>
-        <v>181.61</v>
+        <v>182.88</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="2"/>
-        <v>186.69</v>
+        <v>185.42000000000002</v>
       </c>
       <c r="I31" s="3"/>
     </row>
@@ -1344,356 +1338,314 @@
         <v>31</v>
       </c>
       <c r="C32" s="3">
-        <f>D31</f>
-        <v>163.82999999999998</v>
+        <f>C34*2.54</f>
+        <v>162.56</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" ref="D32:H32" si="3">E31</f>
+        <f t="shared" si="2"/>
         <v>170.18</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>175.26</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="3"/>
-        <v>181.61</v>
+        <f t="shared" si="2"/>
+        <v>180.34</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" si="3"/>
-        <v>186.69</v>
+        <f t="shared" si="2"/>
+        <v>187.96</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>193.04</v>
       </c>
       <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C33">
-        <f>C35*2.54</f>
-        <v>154.94</v>
+        <v>61</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:H34" si="4">D35*2.54</f>
-        <v>165.1</v>
+        <v>65</v>
       </c>
       <c r="E33">
-        <f t="shared" si="4"/>
-        <v>170.18</v>
+        <v>67</v>
       </c>
       <c r="F33">
-        <f t="shared" si="4"/>
-        <v>175.26</v>
+        <v>69</v>
       </c>
       <c r="G33">
-        <f t="shared" si="4"/>
-        <v>182.88</v>
+        <v>72</v>
       </c>
       <c r="H33">
-        <f t="shared" si="4"/>
-        <v>185.42000000000002</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>79</v>
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
       </c>
       <c r="C34">
-        <f>C36*2.54</f>
-        <v>162.56</v>
+        <v>64</v>
       </c>
       <c r="D34">
-        <f t="shared" si="4"/>
-        <v>170.18</v>
+        <v>67</v>
       </c>
       <c r="E34">
-        <f t="shared" si="4"/>
-        <v>175.26</v>
+        <v>69</v>
       </c>
       <c r="F34">
-        <f t="shared" si="4"/>
-        <v>180.34</v>
+        <v>71</v>
       </c>
       <c r="G34">
-        <f t="shared" si="4"/>
-        <v>187.96</v>
+        <v>74</v>
       </c>
       <c r="H34">
-        <f t="shared" si="4"/>
-        <v>193.04</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C35">
-        <v>61</v>
-      </c>
-      <c r="D35">
-        <v>65</v>
-      </c>
-      <c r="E35">
-        <v>67</v>
-      </c>
-      <c r="F35">
+      <c r="A35" t="s">
         <v>69</v>
       </c>
-      <c r="G35">
-        <v>72</v>
-      </c>
-      <c r="H35">
-        <v>73</v>
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36">
-        <v>64</v>
-      </c>
-      <c r="D36">
-        <v>67</v>
-      </c>
-      <c r="E36">
-        <v>69</v>
-      </c>
-      <c r="F36">
-        <v>71</v>
-      </c>
-      <c r="G36">
-        <v>74</v>
-      </c>
-      <c r="H36">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" t="s">
-        <v>90</v>
-      </c>
-      <c r="F37" t="s">
-        <v>91</v>
-      </c>
-      <c r="G37" t="s">
-        <v>92</v>
-      </c>
-      <c r="H37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I37" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
+        <v>35</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>76</v>
+        <v>37</v>
+      </c>
+      <c r="B41">
+        <f>2.6*25.4</f>
+        <v>66.039999999999992</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43">
-        <f>2.6*25.4</f>
-        <v>66.039999999999992</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45">
-        <v>100</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="B47">
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="B48">
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49">
-        <v>148</v>
+        <v>45</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50">
-        <v>110</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
+      </c>
+      <c r="B51">
+        <v>30.9</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53">
-        <v>30.9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>60</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>61</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>76</v>
@@ -1701,7 +1653,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>76</v>
@@ -1709,7 +1661,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>76</v>
@@ -1717,55 +1669,39 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="B69">
+        <v>5700</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71">
-        <v>5700</v>
+        <v>67</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>67</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>68</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>116</v>
-      </c>
-      <c r="B75" t="s">
-        <v>117</v>
+        <v>113</v>
+      </c>
+      <c r="B73" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Wilde Dream Engine Ti 2025.xlsx
+++ b/data/gravel/Wilde Dream Engine Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEAE811-DE2F-2547-8566-C6B625A045AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1404DAC-A40C-C648-A32C-7A92D5572790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,24 @@
   </si>
   <si>
     <t>a8:h32</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -724,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1530,122 +1548,107 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <v>30.9</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B57">
+        <v>30.9</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>76</v>
@@ -1653,36 +1656,36 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B69">
-        <v>5700</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>76</v>
@@ -1690,17 +1693,62 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>113</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>114</v>
       </c>
     </row>

--- a/data/gravel/Wilde Dream Engine Ti 2025.xlsx
+++ b/data/gravel/Wilde Dream Engine Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1404DAC-A40C-C648-A32C-7A92D5572790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDC169E-D357-354B-8B64-88E065D2A79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -380,9 +380,6 @@
     <t>Minneapolis, Minnesota, USA</t>
   </si>
   <si>
-    <t>a8:h32</t>
-  </si>
-  <si>
     <t>head_tube_d</t>
   </si>
   <si>
@@ -399,6 +396,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>a8:h34</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>built around Salsa Cutthroat fork</t>
   </si>
 </sst>
 </file>
@@ -742,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -798,7 +807,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1060,6 +1069,9 @@
       <c r="H17">
         <v>483</v>
       </c>
+      <c r="I17" s="1" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -1197,503 +1209,533 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28">
-        <v>650</v>
-      </c>
-      <c r="D28">
-        <v>650</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
-      </c>
-      <c r="F28">
-        <v>700</v>
-      </c>
-      <c r="G28">
-        <v>700</v>
-      </c>
-      <c r="H28">
-        <v>700</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>650</v>
+      </c>
+      <c r="D30">
+        <v>650</v>
+      </c>
+      <c r="E30">
+        <v>700</v>
+      </c>
+      <c r="F30">
+        <v>700</v>
+      </c>
+      <c r="G30">
+        <v>700</v>
+      </c>
+      <c r="H30">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>28</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="D29">
-        <f t="shared" ref="D29:H29" si="0">2.6*25.4</f>
+      <c r="D31">
+        <f t="shared" ref="D31:H31" si="0">2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <f t="shared" si="0"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="F29">
+      <c r="F31">
         <f t="shared" si="0"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="G29">
+      <c r="G31">
         <f t="shared" si="0"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="H29">
+      <c r="H31">
         <f t="shared" si="0"/>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>29</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="D30">
-        <f t="shared" ref="D30:H30" si="1">2.6*25.4</f>
+      <c r="D32">
+        <f t="shared" ref="D32:H32" si="1">2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <f t="shared" si="1"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <f t="shared" si="1"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="G30">
+      <c r="G32">
         <f t="shared" si="1"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="H30">
+      <c r="H32">
         <f t="shared" si="1"/>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="3">
-        <f>C33*2.54</f>
+      <c r="C33" s="3">
+        <f>C35*2.54</f>
         <v>154.94</v>
       </c>
-      <c r="D31" s="3">
-        <f t="shared" ref="D31:H32" si="2">D33*2.54</f>
+      <c r="D33" s="3">
+        <f t="shared" ref="D33:H34" si="2">D35*2.54</f>
         <v>165.1</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E33" s="3">
         <f t="shared" si="2"/>
         <v>170.18</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F33" s="3">
         <f t="shared" si="2"/>
         <v>175.26</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G33" s="3">
         <f t="shared" si="2"/>
         <v>182.88</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H33" s="3">
         <f t="shared" si="2"/>
         <v>185.42000000000002</v>
       </c>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="3">
-        <f>C34*2.54</f>
+      <c r="C34" s="3">
+        <f>C36*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D34" s="3">
         <f t="shared" si="2"/>
         <v>170.18</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E34" s="3">
         <f t="shared" si="2"/>
         <v>175.26</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F34" s="3">
         <f t="shared" si="2"/>
         <v>180.34</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G34" s="3">
         <f t="shared" si="2"/>
         <v>187.96</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H34" s="3">
         <f t="shared" si="2"/>
         <v>193.04</v>
       </c>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C33">
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C35">
         <v>61</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <v>65</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <v>67</v>
       </c>
-      <c r="F33">
+      <c r="F35">
         <v>69</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <v>72</v>
       </c>
-      <c r="H33">
+      <c r="H35">
         <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34">
-        <v>64</v>
-      </c>
-      <c r="D34">
-        <v>67</v>
-      </c>
-      <c r="E34">
-        <v>69</v>
-      </c>
-      <c r="F34">
-        <v>71</v>
-      </c>
-      <c r="G34">
-        <v>74</v>
-      </c>
-      <c r="H34">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" t="s">
-        <v>89</v>
-      </c>
-      <c r="G35" t="s">
-        <v>90</v>
-      </c>
-      <c r="H35" t="s">
-        <v>91</v>
-      </c>
-      <c r="I35" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36">
+        <v>64</v>
+      </c>
+      <c r="D36">
+        <v>67</v>
+      </c>
+      <c r="E36">
+        <v>69</v>
+      </c>
+      <c r="F36">
         <v>71</v>
       </c>
-      <c r="B36" t="s">
-        <v>72</v>
+      <c r="G36">
+        <v>74</v>
+      </c>
+      <c r="H36">
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" t="s">
+        <v>87</v>
+      </c>
+      <c r="E37" t="s">
+        <v>88</v>
+      </c>
+      <c r="F37" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" t="s">
+        <v>90</v>
+      </c>
+      <c r="H37" t="s">
+        <v>91</v>
+      </c>
+      <c r="I37" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>107</v>
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>34</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>37</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43">
-        <v>100</v>
-      </c>
-    </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B45">
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <v>148</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>110</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>44</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57">
-        <v>30.9</v>
+        <v>45</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="B59">
+        <v>30.9</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>76</v>
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>76</v>
@@ -1701,7 +1743,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>76</v>
@@ -1709,7 +1751,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>76</v>
@@ -1717,38 +1759,54 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75">
-        <v>5700</v>
+        <v>63</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>5700</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>113</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B81" t="s">
         <v>114</v>
       </c>
     </row>
